--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NEW_YORK_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NEW_YORK_2017.xlsx
@@ -2047,7 +2047,7 @@
         <v>25</v>
       </c>
       <c r="D94">
-        <v>0.0009044862518089725</v>
+        <v>0.0009044862518089724</v>
       </c>
     </row>
     <row r="95">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C224">
@@ -6979,7 +6979,7 @@
         <v>25</v>
       </c>
       <c r="D368">
-        <v>0.0009044862518089725</v>
+        <v>0.0009044862518089724</v>
       </c>
     </row>
     <row r="369">
@@ -11371,7 +11371,7 @@
         <v>25</v>
       </c>
       <c r="D612">
-        <v>0.0009044862518089725</v>
+        <v>0.0009044862518089724</v>
       </c>
     </row>
     <row r="613">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C679">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C731">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C732">
@@ -16375,7 +16375,7 @@
         <v>25</v>
       </c>
       <c r="D890">
-        <v>0.0009044862518089725</v>
+        <v>0.0009044862518089724</v>
       </c>
     </row>
     <row r="891">
@@ -17977,7 +17977,7 @@
         <v>25</v>
       </c>
       <c r="D979">
-        <v>0.0009044862518089725</v>
+        <v>0.0009044862518089724</v>
       </c>
     </row>
     <row r="980">
@@ -19651,7 +19651,7 @@
         <v>25</v>
       </c>
       <c r="D1072">
-        <v>0.0009044862518089725</v>
+        <v>0.0009044862518089724</v>
       </c>
     </row>
     <row r="1073">
@@ -22045,7 +22045,7 @@
         <v>25</v>
       </c>
       <c r="D1205">
-        <v>0.0009044862518089725</v>
+        <v>0.0009044862518089724</v>
       </c>
     </row>
     <row r="1206">
@@ -24007,7 +24007,7 @@
         <v>25</v>
       </c>
       <c r="D1314">
-        <v>0.0009044862518089725</v>
+        <v>0.0009044862518089724</v>
       </c>
     </row>
     <row r="1315">
